--- a/registration_forms/039_registration_for_food_for_thought--registration_forms.xlsx
+++ b/registration_forms/039_registration_for_food_for_thought--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'role',_'label':_'role',_'value':_'financial_analyst'}</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'role', 'label': 'role', 'value': 'Financial Analyst'}</t>
+          <t>role</t>
         </is>
       </c>
     </row>
@@ -849,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'role',_'label':_'role',_'value':_'software_developer'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'role', 'label': 'role', 'value': 'Software Developer'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_1_choices</t>
+          <t>select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'role',_'label':_'role',_'value':_'other'}</t>
+          <t>skill1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'role', 'label': 'role', 'value': 'Other'}</t>
+          <t>skill1</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'skill1',_'label':_'skill1',_'value':_'excel'}</t>
+          <t>skill2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'skill1', 'label': 'skill1', 'value': 'Excel'}</t>
+          <t>skill2</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'skill2',_'label':_'skill2',_'value':_'python'}</t>
+          <t>skill3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'skill2', 'label': 'skill2', 'value': 'Python'}</t>
+          <t>skill3</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'skill3',_'label':_'skill3',_'value':_'java'}</t>
+          <t>skill4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'skill3', 'label': 'skill3', 'value': 'Java'}</t>
+          <t>skill4</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'skill4',_'label':_'skill4',_'value':_'c++'}</t>
+          <t>skill5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'skill4', 'label': 'skill4', 'value': 'C++'}</t>
+          <t>skill5</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'skill5',_'label':_'skill5',_'value':_'html'}</t>
+          <t>skill6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'skill5', 'label': 'skill5', 'value': 'HTML'}</t>
+          <t>skill6</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'skill6',_'label':_'skill6',_'value':_'css'}</t>
+          <t>skill7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'skill6', 'label': 'skill6', 'value': 'CSS'}</t>
+          <t>skill7</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'skill7',_'label':_'skill7',_'value':_'other'}</t>
+          <t>skill8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'skill7', 'label': 'skill7', 'value': 'Other'}</t>
+          <t>skill8</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'skill8',_'label':_'skill8',_'value':_'database'}</t>
+          <t>skill9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'skill8', 'label': 'skill8', 'value': 'Database'}</t>
+          <t>skill9</t>
         </is>
       </c>
     </row>
@@ -1019,29 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'skill9',_'label':_'skill9',_'value':_'javascript'}</t>
+          <t>skill10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'skill9', 'label': 'skill9', 'value': 'JavaScript'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple_1_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_23,_'name':_'skill10',_'label':_'skill10',_'value':_'sql'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 23, 'name': 'skill10', 'label': 'skill10', 'value': 'SQL'}</t>
+          <t>skill10</t>
         </is>
       </c>
     </row>
